--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123881345</v>
       </c>
       <c r="B2" t="n">
-        <v>94906</v>
+        <v>94908</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123881345</v>
       </c>
       <c r="B2" t="n">
-        <v>94908</v>
+        <v>95416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322551</v>
+        <v>124322552</v>
       </c>
       <c r="B3" t="n">
-        <v>95438</v>
+        <v>95434</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322534</v>
+        <v>124322551</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>95438</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>2668</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338073</v>
+        <v>338159</v>
       </c>
       <c r="R4" t="n">
-        <v>6532803</v>
+        <v>6532899</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322553</v>
+        <v>124322534</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338075</v>
+        <v>338073</v>
       </c>
       <c r="R5" t="n">
-        <v>6532942</v>
+        <v>6532803</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124322535</v>
+        <v>124322568</v>
       </c>
       <c r="B6" t="n">
-        <v>95434</v>
+        <v>100279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338083</v>
+        <v>338077</v>
       </c>
       <c r="R6" t="n">
-        <v>6532827</v>
+        <v>6532804</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124322552</v>
+        <v>124322535</v>
       </c>
       <c r="B7" t="n">
         <v>95434</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338159</v>
+        <v>338083</v>
       </c>
       <c r="R7" t="n">
-        <v>6532899</v>
+        <v>6532827</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124322549</v>
+        <v>124322553</v>
       </c>
       <c r="B8" t="n">
         <v>100279</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338173</v>
+        <v>338075</v>
       </c>
       <c r="R8" t="n">
-        <v>6532909</v>
+        <v>6532942</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124322568</v>
+        <v>124322549</v>
       </c>
       <c r="B10" t="n">
         <v>100279</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338077</v>
+        <v>338173</v>
       </c>
       <c r="R10" t="n">
-        <v>6532804</v>
+        <v>6532909</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322552</v>
+        <v>124322551</v>
       </c>
       <c r="B3" t="n">
-        <v>95434</v>
+        <v>95438</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322551</v>
+        <v>124322537</v>
       </c>
       <c r="B4" t="n">
-        <v>95438</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2668</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338159</v>
+        <v>338123</v>
       </c>
       <c r="R4" t="n">
-        <v>6532899</v>
+        <v>6532862</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322534</v>
+        <v>124322568</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338073</v>
+        <v>338077</v>
       </c>
       <c r="R5" t="n">
-        <v>6532803</v>
+        <v>6532804</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124322568</v>
+        <v>124322553</v>
       </c>
       <c r="B6" t="n">
         <v>100279</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338077</v>
+        <v>338075</v>
       </c>
       <c r="R6" t="n">
-        <v>6532804</v>
+        <v>6532942</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124322535</v>
+        <v>124322552</v>
       </c>
       <c r="B7" t="n">
         <v>95434</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338083</v>
+        <v>338159</v>
       </c>
       <c r="R7" t="n">
-        <v>6532827</v>
+        <v>6532899</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124322553</v>
+        <v>124322549</v>
       </c>
       <c r="B8" t="n">
         <v>100279</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338075</v>
+        <v>338173</v>
       </c>
       <c r="R8" t="n">
-        <v>6532942</v>
+        <v>6532909</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124322537</v>
+        <v>124322535</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>95434</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338123</v>
+        <v>338083</v>
       </c>
       <c r="R9" t="n">
-        <v>6532862</v>
+        <v>6532827</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124322549</v>
+        <v>124322534</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338173</v>
+        <v>338073</v>
       </c>
       <c r="R10" t="n">
-        <v>6532909</v>
+        <v>6532803</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322551</v>
+        <v>124322549</v>
       </c>
       <c r="B3" t="n">
-        <v>95438</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2668</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338159</v>
+        <v>338173</v>
       </c>
       <c r="R3" t="n">
-        <v>6532899</v>
+        <v>6532909</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322537</v>
+        <v>124322552</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>95434</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338123</v>
+        <v>338159</v>
       </c>
       <c r="R4" t="n">
-        <v>6532862</v>
+        <v>6532899</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322568</v>
+        <v>124322551</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>95438</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>2668</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338077</v>
+        <v>338159</v>
       </c>
       <c r="R5" t="n">
-        <v>6532804</v>
+        <v>6532899</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124322553</v>
+        <v>124322534</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338075</v>
+        <v>338073</v>
       </c>
       <c r="R6" t="n">
-        <v>6532942</v>
+        <v>6532803</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124322552</v>
+        <v>124322535</v>
       </c>
       <c r="B7" t="n">
         <v>95434</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338159</v>
+        <v>338083</v>
       </c>
       <c r="R7" t="n">
-        <v>6532899</v>
+        <v>6532827</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124322549</v>
+        <v>124322553</v>
       </c>
       <c r="B8" t="n">
         <v>100279</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338173</v>
+        <v>338075</v>
       </c>
       <c r="R8" t="n">
-        <v>6532909</v>
+        <v>6532942</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124322535</v>
+        <v>124322537</v>
       </c>
       <c r="B9" t="n">
-        <v>95434</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338083</v>
+        <v>338123</v>
       </c>
       <c r="R9" t="n">
-        <v>6532827</v>
+        <v>6532862</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124322534</v>
+        <v>124322568</v>
       </c>
       <c r="B10" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338073</v>
+        <v>338077</v>
       </c>
       <c r="R10" t="n">
-        <v>6532803</v>
+        <v>6532804</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322549</v>
+        <v>124322535</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>95434</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338173</v>
+        <v>338083</v>
       </c>
       <c r="R3" t="n">
-        <v>6532909</v>
+        <v>6532827</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322552</v>
+        <v>124322537</v>
       </c>
       <c r="B4" t="n">
-        <v>95434</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338159</v>
+        <v>338123</v>
       </c>
       <c r="R4" t="n">
-        <v>6532899</v>
+        <v>6532862</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322551</v>
+        <v>124322549</v>
       </c>
       <c r="B5" t="n">
-        <v>95438</v>
+        <v>100279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2668</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338159</v>
+        <v>338173</v>
       </c>
       <c r="R5" t="n">
-        <v>6532899</v>
+        <v>6532909</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124322534</v>
+        <v>124322552</v>
       </c>
       <c r="B6" t="n">
-        <v>105117</v>
+        <v>95434</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338073</v>
+        <v>338159</v>
       </c>
       <c r="R6" t="n">
-        <v>6532803</v>
+        <v>6532899</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124322535</v>
+        <v>124322551</v>
       </c>
       <c r="B7" t="n">
-        <v>95434</v>
+        <v>95438</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338083</v>
+        <v>338159</v>
       </c>
       <c r="R7" t="n">
-        <v>6532827</v>
+        <v>6532899</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124322537</v>
+        <v>124322568</v>
       </c>
       <c r="B9" t="n">
         <v>100279</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338123</v>
+        <v>338077</v>
       </c>
       <c r="R9" t="n">
-        <v>6532862</v>
+        <v>6532804</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124322568</v>
+        <v>124322534</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338077</v>
+        <v>338073</v>
       </c>
       <c r="R10" t="n">
-        <v>6532804</v>
+        <v>6532803</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322537</v>
+        <v>124322553</v>
       </c>
       <c r="B4" t="n">
         <v>100279</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338123</v>
+        <v>338075</v>
       </c>
       <c r="R4" t="n">
-        <v>6532862</v>
+        <v>6532942</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322549</v>
+        <v>124322537</v>
       </c>
       <c r="B5" t="n">
         <v>100279</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338173</v>
+        <v>338123</v>
       </c>
       <c r="R5" t="n">
-        <v>6532909</v>
+        <v>6532862</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124322552</v>
+        <v>124322551</v>
       </c>
       <c r="B6" t="n">
-        <v>95434</v>
+        <v>95438</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124322551</v>
+        <v>124322568</v>
       </c>
       <c r="B7" t="n">
-        <v>95438</v>
+        <v>100279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2668</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338159</v>
+        <v>338077</v>
       </c>
       <c r="R7" t="n">
-        <v>6532899</v>
+        <v>6532804</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124322553</v>
+        <v>124322552</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>95434</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338075</v>
+        <v>338159</v>
       </c>
       <c r="R8" t="n">
-        <v>6532942</v>
+        <v>6532899</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124322568</v>
+        <v>124322534</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338077</v>
+        <v>338073</v>
       </c>
       <c r="R9" t="n">
-        <v>6532804</v>
+        <v>6532803</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124322534</v>
+        <v>124322549</v>
       </c>
       <c r="B10" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338073</v>
+        <v>338173</v>
       </c>
       <c r="R10" t="n">
-        <v>6532803</v>
+        <v>6532909</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322535</v>
+        <v>124322552</v>
       </c>
       <c r="B3" t="n">
         <v>95434</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338083</v>
+        <v>338159</v>
       </c>
       <c r="R3" t="n">
-        <v>6532827</v>
+        <v>6532899</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322553</v>
+        <v>124322534</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338075</v>
+        <v>338073</v>
       </c>
       <c r="R4" t="n">
-        <v>6532942</v>
+        <v>6532803</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322537</v>
+        <v>124322551</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>95438</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>2668</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338123</v>
+        <v>338159</v>
       </c>
       <c r="R5" t="n">
-        <v>6532862</v>
+        <v>6532899</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124322551</v>
+        <v>124322568</v>
       </c>
       <c r="B6" t="n">
-        <v>95438</v>
+        <v>100279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2668</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338159</v>
+        <v>338077</v>
       </c>
       <c r="R6" t="n">
-        <v>6532899</v>
+        <v>6532804</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124322568</v>
+        <v>124322537</v>
       </c>
       <c r="B7" t="n">
         <v>100279</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338077</v>
+        <v>338123</v>
       </c>
       <c r="R7" t="n">
-        <v>6532804</v>
+        <v>6532862</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124322552</v>
+        <v>124322553</v>
       </c>
       <c r="B8" t="n">
-        <v>95434</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338159</v>
+        <v>338075</v>
       </c>
       <c r="R8" t="n">
-        <v>6532899</v>
+        <v>6532942</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124322534</v>
+        <v>124322535</v>
       </c>
       <c r="B9" t="n">
-        <v>105117</v>
+        <v>95434</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338073</v>
+        <v>338083</v>
       </c>
       <c r="R9" t="n">
-        <v>6532803</v>
+        <v>6532827</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322552</v>
+        <v>124322551</v>
       </c>
       <c r="B3" t="n">
-        <v>95434</v>
+        <v>95438</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322534</v>
+        <v>124322553</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338073</v>
+        <v>338075</v>
       </c>
       <c r="R4" t="n">
-        <v>6532803</v>
+        <v>6532942</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322551</v>
+        <v>124322534</v>
       </c>
       <c r="B5" t="n">
-        <v>95438</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2668</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338159</v>
+        <v>338073</v>
       </c>
       <c r="R5" t="n">
-        <v>6532899</v>
+        <v>6532803</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124322537</v>
+        <v>124322535</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>95434</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338123</v>
+        <v>338083</v>
       </c>
       <c r="R7" t="n">
-        <v>6532862</v>
+        <v>6532827</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124322553</v>
+        <v>124322537</v>
       </c>
       <c r="B8" t="n">
         <v>100279</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338075</v>
+        <v>338123</v>
       </c>
       <c r="R8" t="n">
-        <v>6532942</v>
+        <v>6532862</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124322535</v>
+        <v>124322549</v>
       </c>
       <c r="B9" t="n">
-        <v>95434</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338083</v>
+        <v>338173</v>
       </c>
       <c r="R9" t="n">
-        <v>6532827</v>
+        <v>6532909</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124322549</v>
+        <v>124322552</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>95434</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338173</v>
+        <v>338159</v>
       </c>
       <c r="R10" t="n">
-        <v>6532909</v>
+        <v>6532899</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322551</v>
+        <v>124322535</v>
       </c>
       <c r="B3" t="n">
-        <v>95438</v>
+        <v>95434</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338159</v>
+        <v>338083</v>
       </c>
       <c r="R3" t="n">
-        <v>6532899</v>
+        <v>6532827</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322534</v>
+        <v>124322568</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338073</v>
+        <v>338077</v>
       </c>
       <c r="R5" t="n">
-        <v>6532803</v>
+        <v>6532804</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124322568</v>
+        <v>124322552</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
+        <v>95434</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338077</v>
+        <v>338159</v>
       </c>
       <c r="R6" t="n">
-        <v>6532804</v>
+        <v>6532899</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124322535</v>
+        <v>124322534</v>
       </c>
       <c r="B7" t="n">
-        <v>95434</v>
+        <v>105117</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2667</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338083</v>
+        <v>338073</v>
       </c>
       <c r="R7" t="n">
-        <v>6532827</v>
+        <v>6532803</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124322552</v>
+        <v>124322551</v>
       </c>
       <c r="B10" t="n">
-        <v>95434</v>
+        <v>95438</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322535</v>
+        <v>124322552</v>
       </c>
       <c r="B3" t="n">
         <v>95434</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338083</v>
+        <v>338159</v>
       </c>
       <c r="R3" t="n">
-        <v>6532827</v>
+        <v>6532899</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322553</v>
+        <v>124322535</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>95434</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338075</v>
+        <v>338083</v>
       </c>
       <c r="R4" t="n">
-        <v>6532942</v>
+        <v>6532827</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322568</v>
+        <v>124322537</v>
       </c>
       <c r="B5" t="n">
         <v>100279</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338077</v>
+        <v>338123</v>
       </c>
       <c r="R5" t="n">
-        <v>6532804</v>
+        <v>6532862</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124322552</v>
+        <v>124322551</v>
       </c>
       <c r="B6" t="n">
-        <v>95434</v>
+        <v>95438</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124322534</v>
+        <v>124322553</v>
       </c>
       <c r="B7" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338073</v>
+        <v>338075</v>
       </c>
       <c r="R7" t="n">
-        <v>6532803</v>
+        <v>6532942</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124322537</v>
+        <v>124322549</v>
       </c>
       <c r="B8" t="n">
         <v>100279</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338123</v>
+        <v>338173</v>
       </c>
       <c r="R8" t="n">
-        <v>6532862</v>
+        <v>6532909</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124322549</v>
+        <v>124322568</v>
       </c>
       <c r="B9" t="n">
         <v>100279</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338173</v>
+        <v>338077</v>
       </c>
       <c r="R9" t="n">
-        <v>6532909</v>
+        <v>6532804</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124322551</v>
+        <v>124322534</v>
       </c>
       <c r="B10" t="n">
-        <v>95438</v>
+        <v>105117</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2668</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338159</v>
+        <v>338073</v>
       </c>
       <c r="R10" t="n">
-        <v>6532899</v>
+        <v>6532803</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322552</v>
+        <v>124322568</v>
       </c>
       <c r="B3" t="n">
-        <v>95434</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338159</v>
+        <v>338077</v>
       </c>
       <c r="R3" t="n">
-        <v>6532899</v>
+        <v>6532804</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322535</v>
+        <v>124322549</v>
       </c>
       <c r="B4" t="n">
-        <v>95434</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338083</v>
+        <v>338173</v>
       </c>
       <c r="R4" t="n">
-        <v>6532827</v>
+        <v>6532909</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322537</v>
+        <v>124322534</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338123</v>
+        <v>338073</v>
       </c>
       <c r="R5" t="n">
-        <v>6532862</v>
+        <v>6532803</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124322551</v>
+        <v>124322553</v>
       </c>
       <c r="B6" t="n">
-        <v>95438</v>
+        <v>100279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2668</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338159</v>
+        <v>338075</v>
       </c>
       <c r="R6" t="n">
-        <v>6532899</v>
+        <v>6532942</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124322553</v>
+        <v>124322537</v>
       </c>
       <c r="B7" t="n">
         <v>100279</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338075</v>
+        <v>338123</v>
       </c>
       <c r="R7" t="n">
-        <v>6532942</v>
+        <v>6532862</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124322549</v>
+        <v>124322535</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>95434</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338173</v>
+        <v>338083</v>
       </c>
       <c r="R8" t="n">
-        <v>6532909</v>
+        <v>6532827</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124322568</v>
+        <v>124322551</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>95438</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>2668</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338077</v>
+        <v>338159</v>
       </c>
       <c r="R9" t="n">
-        <v>6532804</v>
+        <v>6532899</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124322534</v>
+        <v>124322552</v>
       </c>
       <c r="B10" t="n">
-        <v>105117</v>
+        <v>95434</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>2667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338073</v>
+        <v>338159</v>
       </c>
       <c r="R10" t="n">
-        <v>6532803</v>
+        <v>6532899</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322568</v>
+        <v>124322537</v>
       </c>
       <c r="B3" t="n">
         <v>100279</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338077</v>
+        <v>338123</v>
       </c>
       <c r="R3" t="n">
-        <v>6532804</v>
+        <v>6532862</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322549</v>
+        <v>124322534</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338173</v>
+        <v>338073</v>
       </c>
       <c r="R4" t="n">
-        <v>6532909</v>
+        <v>6532803</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322534</v>
+        <v>124322552</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>95434</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>2667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338073</v>
+        <v>338159</v>
       </c>
       <c r="R5" t="n">
-        <v>6532803</v>
+        <v>6532899</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124322553</v>
+        <v>124322535</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
+        <v>95434</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338075</v>
+        <v>338083</v>
       </c>
       <c r="R6" t="n">
-        <v>6532942</v>
+        <v>6532827</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124322537</v>
+        <v>124322549</v>
       </c>
       <c r="B7" t="n">
         <v>100279</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338123</v>
+        <v>338173</v>
       </c>
       <c r="R7" t="n">
-        <v>6532862</v>
+        <v>6532909</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124322535</v>
+        <v>124322553</v>
       </c>
       <c r="B8" t="n">
-        <v>95434</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338083</v>
+        <v>338075</v>
       </c>
       <c r="R8" t="n">
-        <v>6532827</v>
+        <v>6532942</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124322551</v>
+        <v>124322568</v>
       </c>
       <c r="B9" t="n">
-        <v>95438</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2668</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338159</v>
+        <v>338077</v>
       </c>
       <c r="R9" t="n">
-        <v>6532899</v>
+        <v>6532804</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124322552</v>
+        <v>124322551</v>
       </c>
       <c r="B10" t="n">
-        <v>95434</v>
+        <v>95438</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322537</v>
+        <v>124322551</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>95438</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2668</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338123</v>
+        <v>338159</v>
       </c>
       <c r="R3" t="n">
-        <v>6532862</v>
+        <v>6532899</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322534</v>
+        <v>124322568</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338073</v>
+        <v>338077</v>
       </c>
       <c r="R4" t="n">
-        <v>6532803</v>
+        <v>6532804</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322552</v>
+        <v>124322537</v>
       </c>
       <c r="B5" t="n">
-        <v>95434</v>
+        <v>100279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338159</v>
+        <v>338123</v>
       </c>
       <c r="R5" t="n">
-        <v>6532899</v>
+        <v>6532862</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124322535</v>
+        <v>124322549</v>
       </c>
       <c r="B6" t="n">
-        <v>95434</v>
+        <v>100279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338083</v>
+        <v>338173</v>
       </c>
       <c r="R6" t="n">
-        <v>6532827</v>
+        <v>6532909</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124322549</v>
+        <v>124322535</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>95434</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338173</v>
+        <v>338083</v>
       </c>
       <c r="R7" t="n">
-        <v>6532909</v>
+        <v>6532827</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124322553</v>
+        <v>124322534</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338075</v>
+        <v>338073</v>
       </c>
       <c r="R8" t="n">
-        <v>6532942</v>
+        <v>6532803</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124322568</v>
+        <v>124322552</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>95434</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338077</v>
+        <v>338159</v>
       </c>
       <c r="R9" t="n">
-        <v>6532804</v>
+        <v>6532899</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124322551</v>
+        <v>124322553</v>
       </c>
       <c r="B10" t="n">
-        <v>95438</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2668</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338159</v>
+        <v>338075</v>
       </c>
       <c r="R10" t="n">
-        <v>6532899</v>
+        <v>6532942</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1596,6 +1596,588 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128465376</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100658</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>338040</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6532900</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128465375</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105514</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>337956</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6532911</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128465381</v>
+      </c>
+      <c r="B13" t="n">
+        <v>95807</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>338115</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6532879</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128465380</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100658</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>338116</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6532879</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128465379</v>
+      </c>
+      <c r="B15" t="n">
+        <v>95809</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2666</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Exsertotheca crispa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>338116</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6532878</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128465366</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100658</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>338079</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6532797</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>128465376</v>
       </c>
       <c r="B11" t="n">
-        <v>100658</v>
+        <v>100660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128465375</v>
       </c>
       <c r="B12" t="n">
-        <v>105514</v>
+        <v>105516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128465381</v>
       </c>
       <c r="B13" t="n">
-        <v>95807</v>
+        <v>95809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>128465380</v>
       </c>
       <c r="B14" t="n">
-        <v>100658</v>
+        <v>100660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128465379</v>
       </c>
       <c r="B15" t="n">
-        <v>95809</v>
+        <v>95811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128465366</v>
       </c>
       <c r="B16" t="n">
-        <v>100658</v>
+        <v>100660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -1698,7 +1698,7 @@
         <v>128465375</v>
       </c>
       <c r="B12" t="n">
-        <v>105516</v>
+        <v>105609</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>128465376</v>
       </c>
       <c r="B11" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128465381</v>
       </c>
       <c r="B13" t="n">
-        <v>95809</v>
+        <v>95902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>128465380</v>
       </c>
       <c r="B14" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128465379</v>
       </c>
       <c r="B15" t="n">
-        <v>95811</v>
+        <v>95904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128465366</v>
       </c>
       <c r="B16" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>128465376</v>
       </c>
       <c r="B11" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128465375</v>
       </c>
       <c r="B12" t="n">
-        <v>105609</v>
+        <v>105621</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128465381</v>
       </c>
       <c r="B13" t="n">
-        <v>95902</v>
+        <v>95908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>128465380</v>
       </c>
       <c r="B14" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128465379</v>
       </c>
       <c r="B15" t="n">
-        <v>95904</v>
+        <v>95910</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128465366</v>
       </c>
       <c r="B16" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>128465376</v>
       </c>
       <c r="B11" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128465375</v>
       </c>
       <c r="B12" t="n">
-        <v>105621</v>
+        <v>105630</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128465381</v>
       </c>
       <c r="B13" t="n">
-        <v>95908</v>
+        <v>95914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>128465380</v>
       </c>
       <c r="B14" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128465379</v>
       </c>
       <c r="B15" t="n">
-        <v>95910</v>
+        <v>95916</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128465366</v>
       </c>
       <c r="B16" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>128465376</v>
       </c>
       <c r="B11" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128465375</v>
       </c>
       <c r="B12" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128465381</v>
       </c>
       <c r="B13" t="n">
-        <v>95914</v>
+        <v>95916</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>128465380</v>
       </c>
       <c r="B14" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128465379</v>
       </c>
       <c r="B15" t="n">
-        <v>95916</v>
+        <v>95918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128465366</v>
       </c>
       <c r="B16" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>128465376</v>
       </c>
       <c r="B11" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128465375</v>
       </c>
       <c r="B12" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>128465380</v>
       </c>
       <c r="B14" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128465366</v>
       </c>
       <c r="B16" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>128465376</v>
       </c>
       <c r="B11" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128465375</v>
       </c>
       <c r="B12" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128465381</v>
       </c>
       <c r="B13" t="n">
-        <v>95916</v>
+        <v>95917</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>128465380</v>
       </c>
       <c r="B14" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128465379</v>
       </c>
       <c r="B15" t="n">
-        <v>95918</v>
+        <v>95919</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128465366</v>
       </c>
       <c r="B16" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>128465376</v>
       </c>
       <c r="B11" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128465375</v>
       </c>
       <c r="B12" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128465381</v>
       </c>
       <c r="B13" t="n">
-        <v>95917</v>
+        <v>95944</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>128465380</v>
       </c>
       <c r="B14" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128465379</v>
       </c>
       <c r="B15" t="n">
-        <v>95919</v>
+        <v>95946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128465366</v>
       </c>
       <c r="B16" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2178,6 +2178,1073 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128877019</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100813</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>338026</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6532849</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128877018</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105688</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>338069</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6532818</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128877033</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100813</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>338147</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6532869</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128877027</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92434</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>338103</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6532844</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128877025</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92434</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>338077</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6532800</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128877022</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100813</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>338022</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6532870</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128877026</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101718</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>338101</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6532818</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128877028</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101718</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>338118</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6532866</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128877024</v>
+      </c>
+      <c r="B25" t="n">
+        <v>95950</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>338075</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6532826</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128877032</v>
+      </c>
+      <c r="B26" t="n">
+        <v>95950</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>338126</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6532860</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128877021</v>
+      </c>
+      <c r="B27" t="n">
+        <v>100813</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>337974</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6532883</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>128465376</v>
       </c>
       <c r="B11" t="n">
-        <v>100807</v>
+        <v>100820</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128465375</v>
       </c>
       <c r="B12" t="n">
-        <v>105682</v>
+        <v>105695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128465381</v>
       </c>
       <c r="B13" t="n">
-        <v>95944</v>
+        <v>95957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>128465380</v>
       </c>
       <c r="B14" t="n">
-        <v>100807</v>
+        <v>100820</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128465379</v>
       </c>
       <c r="B15" t="n">
-        <v>95946</v>
+        <v>95959</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128465366</v>
       </c>
       <c r="B16" t="n">
-        <v>100807</v>
+        <v>100820</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>128877019</v>
       </c>
       <c r="B17" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>128877018</v>
       </c>
       <c r="B18" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>128877033</v>
       </c>
       <c r="B19" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>128877027</v>
       </c>
       <c r="B20" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>128877025</v>
       </c>
       <c r="B21" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128877022</v>
       </c>
       <c r="B22" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>128877026</v>
       </c>
       <c r="B23" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>128877028</v>
       </c>
       <c r="B24" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128877024</v>
       </c>
       <c r="B25" t="n">
-        <v>95950</v>
+        <v>95957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>128877032</v>
       </c>
       <c r="B26" t="n">
-        <v>95950</v>
+        <v>95957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>128877021</v>
       </c>
       <c r="B27" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2859,10 +2859,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128877028</v>
+        <v>128877024</v>
       </c>
       <c r="B24" t="n">
-        <v>101725</v>
+        <v>95957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>2667</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>338118</v>
+        <v>338075</v>
       </c>
       <c r="R24" t="n">
-        <v>6532866</v>
+        <v>6532826</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128877024</v>
+        <v>128877028</v>
       </c>
       <c r="B25" t="n">
-        <v>95957</v>
+        <v>101725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338075</v>
+        <v>338118</v>
       </c>
       <c r="R25" t="n">
-        <v>6532826</v>
+        <v>6532866</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128877019</v>
+        <v>128877018</v>
       </c>
       <c r="B17" t="n">
-        <v>100820</v>
+        <v>105699</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338026</v>
+        <v>338069</v>
       </c>
       <c r="R17" t="n">
-        <v>6532849</v>
+        <v>6532818</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128877018</v>
+        <v>128877019</v>
       </c>
       <c r="B18" t="n">
-        <v>105695</v>
+        <v>100824</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338069</v>
+        <v>338026</v>
       </c>
       <c r="R18" t="n">
-        <v>6532818</v>
+        <v>6532849</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2377,7 +2377,7 @@
         <v>128877033</v>
       </c>
       <c r="B19" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>128877027</v>
       </c>
       <c r="B20" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>128877025</v>
       </c>
       <c r="B21" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128877022</v>
       </c>
       <c r="B22" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>128877026</v>
       </c>
       <c r="B23" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>128877024</v>
       </c>
       <c r="B24" t="n">
-        <v>95957</v>
+        <v>95961</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128877028</v>
       </c>
       <c r="B25" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>128877032</v>
       </c>
       <c r="B26" t="n">
-        <v>95957</v>
+        <v>95961</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>128877021</v>
       </c>
       <c r="B27" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>128465376</v>
       </c>
       <c r="B11" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128465375</v>
       </c>
       <c r="B12" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128465381</v>
       </c>
       <c r="B13" t="n">
-        <v>95957</v>
+        <v>95961</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>128465380</v>
       </c>
       <c r="B14" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128465379</v>
       </c>
       <c r="B15" t="n">
-        <v>95959</v>
+        <v>95963</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128465366</v>
       </c>
       <c r="B16" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>128465376</v>
       </c>
       <c r="B11" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128465375</v>
       </c>
       <c r="B12" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>128465381</v>
       </c>
       <c r="B13" t="n">
-        <v>95961</v>
+        <v>95968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>128465380</v>
       </c>
       <c r="B14" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128465379</v>
       </c>
       <c r="B15" t="n">
-        <v>95963</v>
+        <v>95970</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128465366</v>
       </c>
       <c r="B16" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>128877018</v>
       </c>
       <c r="B17" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>128877019</v>
       </c>
       <c r="B18" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>128877033</v>
       </c>
       <c r="B19" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>128877027</v>
       </c>
       <c r="B20" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>128877025</v>
       </c>
       <c r="B21" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128877022</v>
       </c>
       <c r="B22" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>128877026</v>
       </c>
       <c r="B23" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>128877024</v>
       </c>
       <c r="B24" t="n">
-        <v>95961</v>
+        <v>95968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128877028</v>
       </c>
       <c r="B25" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>128877032</v>
       </c>
       <c r="B26" t="n">
-        <v>95961</v>
+        <v>95968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>128877021</v>
       </c>
       <c r="B27" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128877018</v>
+        <v>128877019</v>
       </c>
       <c r="B17" t="n">
-        <v>105714</v>
+        <v>100844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338069</v>
+        <v>338026</v>
       </c>
       <c r="R17" t="n">
-        <v>6532818</v>
+        <v>6532849</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128877019</v>
+        <v>128877018</v>
       </c>
       <c r="B18" t="n">
-        <v>100839</v>
+        <v>105719</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338026</v>
+        <v>338069</v>
       </c>
       <c r="R18" t="n">
-        <v>6532849</v>
+        <v>6532818</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2377,7 +2377,7 @@
         <v>128877033</v>
       </c>
       <c r="B19" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>128877027</v>
       </c>
       <c r="B20" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>128877025</v>
       </c>
       <c r="B21" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128877022</v>
       </c>
       <c r="B22" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>128877026</v>
       </c>
       <c r="B23" t="n">
-        <v>101744</v>
+        <v>101749</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>128877024</v>
       </c>
       <c r="B24" t="n">
-        <v>95976</v>
+        <v>95981</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128877028</v>
       </c>
       <c r="B25" t="n">
-        <v>101744</v>
+        <v>101749</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>128877032</v>
       </c>
       <c r="B26" t="n">
-        <v>95976</v>
+        <v>95981</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>128877021</v>
       </c>
       <c r="B27" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>128877019</v>
       </c>
       <c r="B17" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>128877018</v>
       </c>
       <c r="B18" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>128877033</v>
       </c>
       <c r="B19" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>128877027</v>
       </c>
       <c r="B20" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>128877025</v>
       </c>
       <c r="B21" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128877022</v>
       </c>
       <c r="B22" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>128877026</v>
       </c>
       <c r="B23" t="n">
-        <v>101749</v>
+        <v>101752</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>128877024</v>
       </c>
       <c r="B24" t="n">
-        <v>95981</v>
+        <v>95984</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128877028</v>
       </c>
       <c r="B25" t="n">
-        <v>101749</v>
+        <v>101752</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>128877032</v>
       </c>
       <c r="B26" t="n">
-        <v>95981</v>
+        <v>95984</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>128877021</v>
       </c>
       <c r="B27" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128877019</v>
+        <v>128877018</v>
       </c>
       <c r="B17" t="n">
-        <v>100847</v>
+        <v>105722</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338026</v>
+        <v>338069</v>
       </c>
       <c r="R17" t="n">
-        <v>6532849</v>
+        <v>6532818</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128877018</v>
+        <v>128877019</v>
       </c>
       <c r="B18" t="n">
-        <v>105722</v>
+        <v>100847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338069</v>
+        <v>338026</v>
       </c>
       <c r="R18" t="n">
-        <v>6532818</v>
+        <v>6532849</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128877024</v>
+        <v>128877028</v>
       </c>
       <c r="B24" t="n">
-        <v>95984</v>
+        <v>101752</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2667</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>338075</v>
+        <v>338118</v>
       </c>
       <c r="R24" t="n">
-        <v>6532826</v>
+        <v>6532866</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128877028</v>
+        <v>128877024</v>
       </c>
       <c r="B25" t="n">
-        <v>101752</v>
+        <v>95984</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338118</v>
+        <v>338075</v>
       </c>
       <c r="R25" t="n">
-        <v>6532866</v>
+        <v>6532826</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128877032</v>
+        <v>128877021</v>
       </c>
       <c r="B26" t="n">
-        <v>95984</v>
+        <v>100847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>338126</v>
+        <v>337974</v>
       </c>
       <c r="R26" t="n">
-        <v>6532860</v>
+        <v>6532883</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128877021</v>
+        <v>128877032</v>
       </c>
       <c r="B27" t="n">
-        <v>100847</v>
+        <v>95984</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3161,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>337974</v>
+        <v>338126</v>
       </c>
       <c r="R27" t="n">
-        <v>6532883</v>
+        <v>6532860</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128877021</v>
+        <v>128877032</v>
       </c>
       <c r="B26" t="n">
-        <v>100847</v>
+        <v>95984</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>337974</v>
+        <v>338126</v>
       </c>
       <c r="R26" t="n">
-        <v>6532883</v>
+        <v>6532860</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128877032</v>
+        <v>128877021</v>
       </c>
       <c r="B27" t="n">
-        <v>95984</v>
+        <v>100847</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3161,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>338126</v>
+        <v>337974</v>
       </c>
       <c r="R27" t="n">
-        <v>6532860</v>
+        <v>6532883</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2859,10 +2859,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128877028</v>
+        <v>128877024</v>
       </c>
       <c r="B24" t="n">
-        <v>101752</v>
+        <v>95984</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>2667</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>338118</v>
+        <v>338075</v>
       </c>
       <c r="R24" t="n">
-        <v>6532866</v>
+        <v>6532826</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128877024</v>
+        <v>128877028</v>
       </c>
       <c r="B25" t="n">
-        <v>95984</v>
+        <v>101752</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338075</v>
+        <v>338118</v>
       </c>
       <c r="R25" t="n">
-        <v>6532826</v>
+        <v>6532866</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128877018</v>
+        <v>128877019</v>
       </c>
       <c r="B17" t="n">
-        <v>105722</v>
+        <v>100857</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338069</v>
+        <v>338026</v>
       </c>
       <c r="R17" t="n">
-        <v>6532818</v>
+        <v>6532849</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128877019</v>
+        <v>128877018</v>
       </c>
       <c r="B18" t="n">
-        <v>100847</v>
+        <v>105732</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338026</v>
+        <v>338069</v>
       </c>
       <c r="R18" t="n">
-        <v>6532849</v>
+        <v>6532818</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2377,7 +2377,7 @@
         <v>128877033</v>
       </c>
       <c r="B19" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>128877027</v>
       </c>
       <c r="B20" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>128877025</v>
       </c>
       <c r="B21" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128877022</v>
       </c>
       <c r="B22" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>128877026</v>
       </c>
       <c r="B23" t="n">
-        <v>101752</v>
+        <v>101762</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128877024</v>
+        <v>128877028</v>
       </c>
       <c r="B24" t="n">
-        <v>95984</v>
+        <v>101762</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2667</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>338075</v>
+        <v>338118</v>
       </c>
       <c r="R24" t="n">
-        <v>6532826</v>
+        <v>6532866</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128877028</v>
+        <v>128877024</v>
       </c>
       <c r="B25" t="n">
-        <v>101752</v>
+        <v>95994</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338118</v>
+        <v>338075</v>
       </c>
       <c r="R25" t="n">
-        <v>6532866</v>
+        <v>6532826</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3056,7 +3056,7 @@
         <v>128877032</v>
       </c>
       <c r="B26" t="n">
-        <v>95984</v>
+        <v>95994</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>128877021</v>
       </c>
       <c r="B27" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>128877019</v>
       </c>
       <c r="B17" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>128877018</v>
       </c>
       <c r="B18" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>128877033</v>
       </c>
       <c r="B19" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>128877027</v>
       </c>
       <c r="B20" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>128877025</v>
       </c>
       <c r="B21" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128877022</v>
       </c>
       <c r="B22" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>128877026</v>
       </c>
       <c r="B23" t="n">
-        <v>101762</v>
+        <v>101769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128877028</v>
+        <v>128877024</v>
       </c>
       <c r="B24" t="n">
-        <v>101762</v>
+        <v>96001</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>2667</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>338118</v>
+        <v>338075</v>
       </c>
       <c r="R24" t="n">
-        <v>6532866</v>
+        <v>6532826</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128877024</v>
+        <v>128877028</v>
       </c>
       <c r="B25" t="n">
-        <v>95994</v>
+        <v>101769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338075</v>
+        <v>338118</v>
       </c>
       <c r="R25" t="n">
-        <v>6532826</v>
+        <v>6532866</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3056,7 +3056,7 @@
         <v>128877032</v>
       </c>
       <c r="B26" t="n">
-        <v>95994</v>
+        <v>96001</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>128877021</v>
       </c>
       <c r="B27" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128877019</v>
+        <v>128877018</v>
       </c>
       <c r="B17" t="n">
-        <v>100864</v>
+        <v>105741</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338026</v>
+        <v>338069</v>
       </c>
       <c r="R17" t="n">
-        <v>6532849</v>
+        <v>6532818</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128877018</v>
+        <v>128877019</v>
       </c>
       <c r="B18" t="n">
-        <v>105739</v>
+        <v>100866</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338069</v>
+        <v>338026</v>
       </c>
       <c r="R18" t="n">
-        <v>6532818</v>
+        <v>6532849</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2377,7 +2377,7 @@
         <v>128877033</v>
       </c>
       <c r="B19" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>128877027</v>
       </c>
       <c r="B20" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>128877025</v>
       </c>
       <c r="B21" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128877022</v>
       </c>
       <c r="B22" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>128877026</v>
       </c>
       <c r="B23" t="n">
-        <v>101769</v>
+        <v>101771</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>128877024</v>
       </c>
       <c r="B24" t="n">
-        <v>96001</v>
+        <v>96003</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128877028</v>
       </c>
       <c r="B25" t="n">
-        <v>101769</v>
+        <v>101771</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>128877032</v>
       </c>
       <c r="B26" t="n">
-        <v>96001</v>
+        <v>96003</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>128877021</v>
       </c>
       <c r="B27" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128877018</v>
+        <v>128877019</v>
       </c>
       <c r="B17" t="n">
-        <v>105741</v>
+        <v>100866</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338069</v>
+        <v>338026</v>
       </c>
       <c r="R17" t="n">
-        <v>6532818</v>
+        <v>6532849</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128877019</v>
+        <v>128877018</v>
       </c>
       <c r="B18" t="n">
-        <v>100866</v>
+        <v>105741</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338026</v>
+        <v>338069</v>
       </c>
       <c r="R18" t="n">
-        <v>6532849</v>
+        <v>6532818</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128877032</v>
+        <v>128877021</v>
       </c>
       <c r="B26" t="n">
-        <v>96003</v>
+        <v>100866</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>338126</v>
+        <v>337974</v>
       </c>
       <c r="R26" t="n">
-        <v>6532860</v>
+        <v>6532883</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128877021</v>
+        <v>128877032</v>
       </c>
       <c r="B27" t="n">
-        <v>100866</v>
+        <v>96003</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3161,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>337974</v>
+        <v>338126</v>
       </c>
       <c r="R27" t="n">
-        <v>6532883</v>
+        <v>6532860</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128877019</v>
+        <v>128877018</v>
       </c>
       <c r="B17" t="n">
-        <v>100866</v>
+        <v>105767</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338026</v>
+        <v>338069</v>
       </c>
       <c r="R17" t="n">
-        <v>6532849</v>
+        <v>6532818</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128877018</v>
+        <v>128877019</v>
       </c>
       <c r="B18" t="n">
-        <v>105741</v>
+        <v>100892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338069</v>
+        <v>338026</v>
       </c>
       <c r="R18" t="n">
-        <v>6532818</v>
+        <v>6532849</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2377,7 +2377,7 @@
         <v>128877033</v>
       </c>
       <c r="B19" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>128877027</v>
       </c>
       <c r="B20" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>128877025</v>
       </c>
       <c r="B21" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128877022</v>
       </c>
       <c r="B22" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>128877026</v>
       </c>
       <c r="B23" t="n">
-        <v>101771</v>
+        <v>101797</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128877024</v>
+        <v>128877028</v>
       </c>
       <c r="B24" t="n">
-        <v>96003</v>
+        <v>101797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2667</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>338075</v>
+        <v>338118</v>
       </c>
       <c r="R24" t="n">
-        <v>6532826</v>
+        <v>6532866</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128877028</v>
+        <v>128877024</v>
       </c>
       <c r="B25" t="n">
-        <v>101771</v>
+        <v>96029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338118</v>
+        <v>338075</v>
       </c>
       <c r="R25" t="n">
-        <v>6532866</v>
+        <v>6532826</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3056,7 +3056,7 @@
         <v>128877021</v>
       </c>
       <c r="B26" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>128877032</v>
       </c>
       <c r="B27" t="n">
-        <v>96003</v>
+        <v>96029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>128877018</v>
       </c>
       <c r="B17" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>128877019</v>
       </c>
       <c r="B18" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>128877033</v>
       </c>
       <c r="B19" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>128877027</v>
       </c>
       <c r="B20" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>128877025</v>
       </c>
       <c r="B21" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128877022</v>
       </c>
       <c r="B22" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>128877026</v>
       </c>
       <c r="B23" t="n">
-        <v>101797</v>
+        <v>101799</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128877028</v>
+        <v>128877024</v>
       </c>
       <c r="B24" t="n">
-        <v>101797</v>
+        <v>96030</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>2667</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>338118</v>
+        <v>338075</v>
       </c>
       <c r="R24" t="n">
-        <v>6532866</v>
+        <v>6532826</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128877024</v>
+        <v>128877028</v>
       </c>
       <c r="B25" t="n">
-        <v>96029</v>
+        <v>101799</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338075</v>
+        <v>338118</v>
       </c>
       <c r="R25" t="n">
-        <v>6532826</v>
+        <v>6532866</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128877021</v>
+        <v>128877032</v>
       </c>
       <c r="B26" t="n">
-        <v>100892</v>
+        <v>96030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>337974</v>
+        <v>338126</v>
       </c>
       <c r="R26" t="n">
-        <v>6532883</v>
+        <v>6532860</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128877032</v>
+        <v>128877021</v>
       </c>
       <c r="B27" t="n">
-        <v>96029</v>
+        <v>100894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3161,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>338126</v>
+        <v>337974</v>
       </c>
       <c r="R27" t="n">
-        <v>6532860</v>
+        <v>6532883</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>128877018</v>
       </c>
       <c r="B17" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>128877019</v>
       </c>
       <c r="B18" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>128877033</v>
       </c>
       <c r="B19" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128877022</v>
       </c>
       <c r="B22" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>128877026</v>
       </c>
       <c r="B23" t="n">
-        <v>101799</v>
+        <v>101800</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>128877024</v>
       </c>
       <c r="B24" t="n">
-        <v>96030</v>
+        <v>96031</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128877028</v>
       </c>
       <c r="B25" t="n">
-        <v>101799</v>
+        <v>101800</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>128877032</v>
       </c>
       <c r="B26" t="n">
-        <v>96030</v>
+        <v>96031</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>128877021</v>
       </c>
       <c r="B27" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128877018</v>
+        <v>128877019</v>
       </c>
       <c r="B17" t="n">
-        <v>105770</v>
+        <v>100899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338069</v>
+        <v>338026</v>
       </c>
       <c r="R17" t="n">
-        <v>6532818</v>
+        <v>6532849</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128877019</v>
+        <v>128877018</v>
       </c>
       <c r="B18" t="n">
-        <v>100895</v>
+        <v>105774</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338026</v>
+        <v>338069</v>
       </c>
       <c r="R18" t="n">
-        <v>6532849</v>
+        <v>6532818</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2377,7 +2377,7 @@
         <v>128877033</v>
       </c>
       <c r="B19" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>128877027</v>
       </c>
       <c r="B20" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>128877025</v>
       </c>
       <c r="B21" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128877022</v>
       </c>
       <c r="B22" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>128877026</v>
       </c>
       <c r="B23" t="n">
-        <v>101800</v>
+        <v>101804</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>128877024</v>
       </c>
       <c r="B24" t="n">
-        <v>96031</v>
+        <v>96035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128877028</v>
       </c>
       <c r="B25" t="n">
-        <v>101800</v>
+        <v>101804</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128877032</v>
+        <v>128877021</v>
       </c>
       <c r="B26" t="n">
-        <v>96031</v>
+        <v>100899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>338126</v>
+        <v>337974</v>
       </c>
       <c r="R26" t="n">
-        <v>6532860</v>
+        <v>6532883</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128877021</v>
+        <v>128877032</v>
       </c>
       <c r="B27" t="n">
-        <v>100895</v>
+        <v>96035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3161,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>337974</v>
+        <v>338126</v>
       </c>
       <c r="R27" t="n">
-        <v>6532883</v>
+        <v>6532860</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -2859,10 +2859,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128877024</v>
+        <v>128877028</v>
       </c>
       <c r="B24" t="n">
-        <v>96035</v>
+        <v>101804</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2667</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>338075</v>
+        <v>338118</v>
       </c>
       <c r="R24" t="n">
-        <v>6532826</v>
+        <v>6532866</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128877028</v>
+        <v>128877024</v>
       </c>
       <c r="B25" t="n">
-        <v>101804</v>
+        <v>96035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2967,21 +2967,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338118</v>
+        <v>338075</v>
       </c>
       <c r="R25" t="n">
-        <v>6532866</v>
+        <v>6532826</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3053,10 +3053,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128877021</v>
+        <v>128877032</v>
       </c>
       <c r="B26" t="n">
-        <v>100899</v>
+        <v>96035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>337974</v>
+        <v>338126</v>
       </c>
       <c r="R26" t="n">
-        <v>6532883</v>
+        <v>6532860</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128877032</v>
+        <v>128877021</v>
       </c>
       <c r="B27" t="n">
-        <v>96035</v>
+        <v>100899</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3161,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>338126</v>
+        <v>337974</v>
       </c>
       <c r="R27" t="n">
-        <v>6532860</v>
+        <v>6532883</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123881345</v>
+        <v>124272739</v>
       </c>
       <c r="B2" t="n">
-        <v>95438</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2668</v>
+        <v>1449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hällebräcka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Saxifraga osloënsis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Knaben</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,17 +710,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skuggetorpsön , Dls</t>
+          <t>Skuggetorpsön, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338149</v>
+        <v>338162</v>
       </c>
       <c r="R2" t="n">
-        <v>6532914</v>
+        <v>6532766</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Niklasson</t>
+          <t>Anders Niklasson, Anton Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322551</v>
+        <v>124322531</v>
       </c>
       <c r="B3" t="n">
-        <v>95438</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338159</v>
+        <v>338162</v>
       </c>
       <c r="R3" t="n">
-        <v>6532899</v>
+        <v>6532776</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322568</v>
+        <v>124322571</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2666</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338077</v>
+        <v>338086</v>
       </c>
       <c r="R4" t="n">
-        <v>6532804</v>
+        <v>6532745</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124322537</v>
+        <v>124322532</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338123</v>
+        <v>338162</v>
       </c>
       <c r="R5" t="n">
-        <v>6532862</v>
+        <v>6532776</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124322549</v>
+        <v>128877013</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338173</v>
+        <v>338138</v>
       </c>
       <c r="R6" t="n">
-        <v>6532909</v>
+        <v>6532778</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1158,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1158,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124322535</v>
+        <v>128877017</v>
       </c>
       <c r="B7" t="n">
-        <v>95434</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338083</v>
+        <v>338057</v>
       </c>
       <c r="R7" t="n">
-        <v>6532827</v>
+        <v>6532790</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1260,12 +1230,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,22 +1255,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124322534</v>
+        <v>124322530</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>2676</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338073</v>
+        <v>338162</v>
       </c>
       <c r="R8" t="n">
-        <v>6532803</v>
+        <v>6532776</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124322552</v>
+        <v>128465358</v>
       </c>
       <c r="B9" t="n">
-        <v>95434</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>2676</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338159</v>
+        <v>338167</v>
       </c>
       <c r="R9" t="n">
-        <v>6532899</v>
+        <v>6532773</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1464,12 +1424,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,22 +1449,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson</t>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124322553</v>
+        <v>128877014</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>2676</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338075</v>
+        <v>338138</v>
       </c>
       <c r="R10" t="n">
-        <v>6532942</v>
+        <v>6532778</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1566,12 +1521,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,17 +1546,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128465376</v>
+        <v>124322570</v>
       </c>
       <c r="B11" t="n">
-        <v>100834</v>
+        <v>96231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338040</v>
+        <v>338087</v>
       </c>
       <c r="R11" t="n">
-        <v>6532900</v>
+        <v>6532744</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1663,12 +1618,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,17 +1643,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+          <t>Anton Larsson, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128465375</v>
+        <v>128877025</v>
       </c>
       <c r="B12" t="n">
-        <v>105709</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>337956</v>
+        <v>338077</v>
       </c>
       <c r="R12" t="n">
-        <v>6532911</v>
+        <v>6532800</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1760,12 +1715,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,17 +1740,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128465381</v>
+        <v>128465365</v>
       </c>
       <c r="B13" t="n">
-        <v>95971</v>
+        <v>5199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,34 +1758,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2667</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skuggetorpsön, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338115</v>
+        <v>338075</v>
       </c>
       <c r="R13" t="n">
-        <v>6532879</v>
+        <v>6532753</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1873,6 +1833,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1889,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128465380</v>
+        <v>124322534</v>
       </c>
       <c r="B14" t="n">
-        <v>100834</v>
+        <v>106244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1900,21 +1875,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338116</v>
+        <v>338073</v>
       </c>
       <c r="R14" t="n">
-        <v>6532879</v>
+        <v>6532803</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1954,12 +1929,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1979,17 +1954,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+          <t>Anton Larsson, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128465379</v>
+        <v>124322568</v>
       </c>
       <c r="B15" t="n">
-        <v>95973</v>
+        <v>101326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +1972,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2666</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338116</v>
+        <v>338077</v>
       </c>
       <c r="R15" t="n">
-        <v>6532878</v>
+        <v>6532804</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2051,12 +2026,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2076,7 +2051,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+          <t>Anton Larsson, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2086,7 +2061,7 @@
         <v>128465366</v>
       </c>
       <c r="B16" t="n">
-        <v>100834</v>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128877019</v>
+        <v>128877000</v>
       </c>
       <c r="B17" t="n">
-        <v>100899</v>
+        <v>85534</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>241</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338026</v>
+        <v>338278</v>
       </c>
       <c r="R17" t="n">
-        <v>6532849</v>
+        <v>6532909</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2261,6 +2236,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2277,32 +2267,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128877018</v>
+        <v>128465368</v>
       </c>
       <c r="B18" t="n">
-        <v>105774</v>
+        <v>102755</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>1879</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Trollsmultron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Drymocallis rupestris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soják</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2302,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338069</v>
+        <v>337984</v>
       </c>
       <c r="R18" t="n">
-        <v>6532818</v>
+        <v>6532825</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2342,12 +2332,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2367,17 +2357,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128877033</v>
+        <v>124322562</v>
       </c>
       <c r="B19" t="n">
-        <v>100899</v>
+        <v>96439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2385,21 +2375,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>2666</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2399,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338147</v>
+        <v>338009</v>
       </c>
       <c r="R19" t="n">
-        <v>6532869</v>
+        <v>6532831</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2439,12 +2429,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2464,17 +2454,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anton Larsson, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128877027</v>
+        <v>128465379</v>
       </c>
       <c r="B20" t="n">
-        <v>92498</v>
+        <v>96439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2482,21 +2472,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>2666</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2506,10 +2496,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>338103</v>
+        <v>338116</v>
       </c>
       <c r="R20" t="n">
-        <v>6532844</v>
+        <v>6532878</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,12 +2526,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2561,17 +2551,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128877025</v>
+        <v>124322535</v>
       </c>
       <c r="B21" t="n">
-        <v>92498</v>
+        <v>96437</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2579,21 +2569,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>2667</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2603,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>338077</v>
+        <v>338083</v>
       </c>
       <c r="R21" t="n">
-        <v>6532800</v>
+        <v>6532827</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2633,12 +2623,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2658,17 +2648,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anton Larsson, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128877022</v>
+        <v>124322552</v>
       </c>
       <c r="B22" t="n">
-        <v>100899</v>
+        <v>96437</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2676,21 +2666,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2700,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>338022</v>
+        <v>338159</v>
       </c>
       <c r="R22" t="n">
-        <v>6532870</v>
+        <v>6532899</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2730,12 +2720,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2755,17 +2745,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anton Larsson, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128877026</v>
+        <v>128465381</v>
       </c>
       <c r="B23" t="n">
-        <v>101804</v>
+        <v>96437</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2773,21 +2763,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221235</v>
+        <v>2667</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2797,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>338101</v>
+        <v>338115</v>
       </c>
       <c r="R23" t="n">
-        <v>6532818</v>
+        <v>6532879</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2827,12 +2817,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2852,17 +2842,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128877028</v>
+        <v>128877024</v>
       </c>
       <c r="B24" t="n">
-        <v>101804</v>
+        <v>96437</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2870,21 +2860,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>2667</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2894,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>338118</v>
+        <v>338075</v>
       </c>
       <c r="R24" t="n">
-        <v>6532866</v>
+        <v>6532826</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2956,10 +2946,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128877024</v>
+        <v>128877032</v>
       </c>
       <c r="B25" t="n">
-        <v>96035</v>
+        <v>96437</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2991,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338075</v>
+        <v>338126</v>
       </c>
       <c r="R25" t="n">
-        <v>6532826</v>
+        <v>6532860</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3053,10 +3043,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128877032</v>
+        <v>123881345</v>
       </c>
       <c r="B26" t="n">
-        <v>96035</v>
+        <v>96441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,37 +3054,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skuggetorpsön, Dls</t>
+          <t>Skuggetorpsön , Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>338126</v>
+        <v>338149</v>
       </c>
       <c r="R26" t="n">
-        <v>6532860</v>
+        <v>6532914</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3118,12 +3112,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3132,28 +3126,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anders Niklasson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anders Niklasson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128877021</v>
+        <v>124322551</v>
       </c>
       <c r="B27" t="n">
-        <v>100899</v>
+        <v>96441</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3156,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>2668</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>337974</v>
+        <v>338159</v>
       </c>
       <c r="R27" t="n">
-        <v>6532883</v>
+        <v>6532899</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3215,12 +3210,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3240,10 +3235,2144 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anton Larsson, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124322564</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96186</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grov baronmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Anomodon viticulosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>338029</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6532814</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124322565</v>
+      </c>
+      <c r="B29" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>338026</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6532815</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128465369</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>338018</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6532826</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128876999</v>
+      </c>
+      <c r="B31" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>338278</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6532909</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124322554</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>337922</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6532876</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>124322559</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>337972</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6532830</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128465372</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>337932</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6532873</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128877027</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>338103</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6532844</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128465375</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>337956</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6532911</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128877018</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>338069</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6532818</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128877026</v>
+      </c>
+      <c r="B38" t="n">
+        <v>102240</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>338101</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6532818</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128877028</v>
+      </c>
+      <c r="B39" t="n">
+        <v>102240</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>338118</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6532866</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124322537</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>338123</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6532862</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124322549</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>338173</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6532909</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124322553</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>338075</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6532942</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128465376</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>338040</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6532900</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128465380</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>338116</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6532879</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128877019</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>338026</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6532849</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128877021</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>337974</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6532883</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128877022</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>338022</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6532870</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128877033</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>338147</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6532869</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128877037</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>338273</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6532873</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11036-2025 artfynd.xlsx
+++ b/artfynd/A 11036-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272739</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465368</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322531</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322562</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322571</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465379</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322532</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322535</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322552</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465381</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877013</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877017</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877024</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877032</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123881345</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322551</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,6 +2533,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322530</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322564</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465358</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2734,6 +2839,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877014</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2831,6 +2941,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322565</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2928,6 +3043,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322570</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3025,6 +3145,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465369</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3122,6 +3247,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128876999</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3219,6 +3349,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322554</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3316,6 +3451,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322559</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3413,6 +3553,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465372</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3510,6 +3655,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3607,6 +3757,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877027</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3724,6 +3879,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465365</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3821,6 +3981,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322534</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3918,6 +4083,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465375</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4015,6 +4185,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877018</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4112,6 +4287,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877026</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4209,6 +4389,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877028</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4306,6 +4491,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322537</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4403,6 +4593,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322549</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4500,6 +4695,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322553</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4597,6 +4797,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322568</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4694,6 +4899,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465366</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4791,6 +5001,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465376</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4888,6 +5103,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465380</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4985,6 +5205,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877019</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5082,6 +5307,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877021</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5179,6 +5409,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877022</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5276,6 +5511,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877033</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5373,8 +5613,63 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877037</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>